--- a/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE7764E-B57A-4815-9FF8-B213EBBD6549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFC062B-6140-40FF-B66E-9CDA2AA8FD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="435" windowWidth="27225" windowHeight="14685" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
   <sheets>
     <sheet name="StartFoodDatas" sheetId="1" r:id="rId1"/>
@@ -206,7 +206,7 @@
     <t>Assets/05.Animations/EffectAnimation/LaserEffect.prefab</t>
   </si>
   <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_m.prefab</t>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_p.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFC062B-6140-40FF-B66E-9CDA2AA8FD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700E97B7-120F-4EB1-BEDA-359A63D8A637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
@@ -203,10 +203,11 @@
     <t>Assets/05.Animations/EffectAnimation/FireEffect.prefab</t>
   </si>
   <si>
-    <t>Assets/05.Animations/EffectAnimation/LaserEffect.prefab</t>
-  </si>
-  <si>
     <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_p.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/05.Animations/EffectAnimation/LaserEffect_2.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -687,7 +688,7 @@
         <v>37</v>
       </c>
       <c r="N2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" t="s">
@@ -862,7 +863,7 @@
       </c>
       <c r="O5" s="1"/>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q5">
         <v>228</v>

--- a/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700E97B7-120F-4EB1-BEDA-359A63D8A637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43EE275-91B2-430F-840F-A3C7E6DB65BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
@@ -667,7 +667,7 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>0.65</v>
@@ -724,7 +724,7 @@
         <v>1.7</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>0.35</v>
@@ -781,7 +781,7 @@
         <v>1.4</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>1.1000000000000001</v>
@@ -838,7 +838,7 @@
         <v>0.85</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>0.25</v>
@@ -895,7 +895,7 @@
         <v>1.9</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>1.1000000000000001</v>

--- a/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43EE275-91B2-430F-840F-A3C7E6DB65BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8CBE83-4F05-40EA-AB9F-B2015E7C3C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
+    <workbookView xWindow="12405" yWindow="405" windowWidth="16125" windowHeight="14685" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
   <sheets>
     <sheet name="StartFoodDatas" sheetId="1" r:id="rId1"/>
@@ -664,13 +664,13 @@
         <v>33</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>34</v>
       </c>
       <c r="F3">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -778,13 +778,13 @@
         <v>16</v>
       </c>
       <c r="F4">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="G4">
         <v>4</v>
       </c>
       <c r="H4">
-        <v>1.1000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -835,13 +835,13 @@
         <v>35</v>
       </c>
       <c r="F5">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -892,7 +892,7 @@
         <v>36</v>
       </c>
       <c r="F6">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="G6">
         <v>4</v>

--- a/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/StartFoodDataSet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8CBE83-4F05-40EA-AB9F-B2015E7C3C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716FFA70-D567-4751-B1FB-AB95381451DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12405" yWindow="405" windowWidth="16125" windowHeight="14685" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
+    <workbookView xWindow="6870" yWindow="345" windowWidth="16125" windowHeight="14685" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
   <sheets>
     <sheet name="StartFoodDatas" sheetId="1" r:id="rId1"/>
@@ -113,14 +113,6 @@
     <t>_EffectPrefabPath</t>
   </si>
   <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/RiceBullet.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/Item/Food1_Item.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>_BulletColor_g</t>
   </si>
   <si>
@@ -181,17 +173,6 @@
   </si>
   <si>
     <t>USA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/Item/Food1_Item.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/SoupBullet.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/BreadBullet.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -200,15 +181,34 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/05.Animations/EffectAnimation/FireEffect.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_p.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/05.Animations/EffectAnimation/LaserEffect_2.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>Bullet/BreadBullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet/RiceBullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet/SoupBullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet/MeatBullet_p</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireEffect</t>
+  </si>
+  <si>
+    <t>FireEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LaserEffect_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food1_Item</t>
   </si>
 </sst>
 </file>
@@ -638,18 +638,18 @@
         <v>18</v>
       </c>
       <c r="Q1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" t="s">
         <v>21</v>
-      </c>
-      <c r="S1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F2">
         <v>3.75</v>
@@ -685,10 +685,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O2" s="1"/>
       <c r="P2" t="s">
@@ -706,7 +706,7 @@
     </row>
     <row r="3" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -715,10 +715,10 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>1.9</v>
@@ -742,14 +742,14 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
         <v>37</v>
-      </c>
-      <c r="N3" t="s">
-        <v>19</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q3">
         <v>140</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="4" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -772,7 +772,7 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -796,17 +796,17 @@
         <v>0</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M4" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
         <v>38</v>
       </c>
       <c r="O4" s="1"/>
       <c r="P4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q4">
         <v>44</v>
@@ -820,7 +820,7 @@
     </row>
     <row r="5" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -832,7 +832,7 @@
         <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>0.95</v>
@@ -856,14 +856,14 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
         <v>37</v>
-      </c>
-      <c r="N5" t="s">
-        <v>19</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q5">
         <v>228</v>
@@ -877,7 +877,7 @@
     </row>
     <row r="6" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -886,10 +886,10 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F6">
         <v>2.8</v>
@@ -913,14 +913,14 @@
         <v>0.8</v>
       </c>
       <c r="M6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q6">
         <v>255</v>
